--- a/testdata/caldata2.xlsx
+++ b/testdata/caldata2.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="19">
   <si>
     <t>Initial Deposit amout</t>
   </si>
@@ -180,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -205,6 +205,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
@@ -551,7 +561,7 @@
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" t="s" s="20">
+      <c r="G2" t="s" s="30">
         <v>18</v>
       </c>
     </row>
@@ -574,7 +584,7 @@
       <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G3" t="s" s="21">
+      <c r="G3" t="s" s="31">
         <v>18</v>
       </c>
     </row>
@@ -597,7 +607,7 @@
       <c r="F4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G4" t="s" s="22">
+      <c r="G4" t="s" s="32">
         <v>18</v>
       </c>
     </row>
@@ -620,7 +630,7 @@
       <c r="F5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" t="s" s="23">
+      <c r="G5" t="s" s="33">
         <v>18</v>
       </c>
     </row>
@@ -643,7 +653,7 @@
       <c r="F6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G6" t="s" s="24">
+      <c r="G6" t="s" s="34">
         <v>17</v>
       </c>
     </row>
